--- a/Cross Reference Matrix/Cross Matrix.xlsx
+++ b/Cross Reference Matrix/Cross Matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70d00439813d2287/Documents/Illinois Tech/Cybersecurity Management/Paper/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\2025 fall\Cybersecurity management\ResearchProgress_Group20\Cross Reference Matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{817CE898-8219-4851-B926-0115F4B9781F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F3F238-D263-47E5-80BE-D3EEAEE2DFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A05D92C0-22AD-402D-B61A-030F20CD21FE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="100">
   <si>
     <r>
       <rPr>
@@ -761,6 +761,67 @@
   </si>
   <si>
     <t>Framework</t>
+  </si>
+  <si>
+    <t>UNESCO AI and Education</t>
+  </si>
+  <si>
+    <t>Education/Academia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">UNESCO AI and Education: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mainly focuses on governance. Specifies how students and teachers should use AI responsibly</t>
+    </r>
+  </si>
+  <si>
+    <t>Education Institutions</t>
+  </si>
+  <si>
+    <t>Family Educational Rights and Privacy Act (FERPA)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FERPA: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Act that protects the private information of students. Defines who can access and share the information and under what conditions</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -829,7 +890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1134,11 +1195,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1146,139 +1292,166 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1614,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48114A91-5777-4F00-84F8-9B4A2B7A4DDC}">
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -1632,1890 +1805,2037 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="J1" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="K1" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="48" t="s">
+      <c r="L1" s="23" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="45" t="s">
+      <c r="E2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="29" t="s">
+      <c r="F3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="28" t="s">
+      <c r="K3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="29" t="s">
+      <c r="E4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="29" t="s">
+      <c r="E5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="29" t="s">
+      <c r="E6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="40" t="s">
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="41" t="s">
+      <c r="E8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="40" t="s">
+      <c r="L8" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="41" t="s">
+      <c r="E9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="36" t="s">
+      <c r="E10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="35" t="s">
+    <row r="11" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="33" t="s">
+      <c r="E12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="32" t="s">
+      <c r="K12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="31" t="s">
+    <row r="13" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="29" t="s">
+      <c r="E13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="29" t="s">
+      <c r="J13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="28" t="s">
+      <c r="L13" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="31" t="s">
+    <row r="14" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="28" t="s">
+      <c r="E14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="31" t="s">
+    <row r="15" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="29" t="s">
+      <c r="E15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="29" t="s">
+      <c r="H15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L14" s="28" t="s">
+      <c r="L15" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="31" t="s">
+    <row r="16" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="28" t="s">
+      <c r="E16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="31" t="s">
+    <row r="17" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D17" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="28" t="s">
+      <c r="E17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="27" t="s">
+    <row r="18" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="24" t="s">
+      <c r="E18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="35" t="s">
+    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="33" t="s">
+      <c r="E19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="33" t="s">
+      <c r="H19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J18" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="33" t="s">
+      <c r="J19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="32" t="s">
+      <c r="L19" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="31" t="s">
+    <row r="20" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C20" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="29" t="s">
+      <c r="E20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K20" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="28" t="s">
+      <c r="L20" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="31" t="s">
+    <row r="21" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B21" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C21" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="29" t="s">
+      <c r="E21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I21" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L20" s="28" t="s">
+      <c r="J21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="31" t="s">
+    <row r="22" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="29" t="s">
+      <c r="E22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="29" t="s">
+      <c r="J22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L22" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="31" t="s">
+    <row r="23" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C23" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="29" t="s">
+      <c r="E23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L23" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="31" t="s">
+    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C24" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D24" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="29" t="s">
+      <c r="E24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I23" s="29" t="s">
+      <c r="I24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J23" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" s="29" t="s">
+      <c r="J24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L24" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B24" s="31" t="s">
+    <row r="25" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B25" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C25" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="29" t="s">
+      <c r="E25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L25" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B25" s="31" t="s">
+    <row r="26" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C26" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E26" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="29" t="s">
+      <c r="F26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J25" s="29" t="s">
+      <c r="J26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K26" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="L26" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="27" t="s">
+    <row r="27" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="K27" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="25" t="s">
+      <c r="F28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="25" t="s">
+      <c r="I28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L26" s="24" t="s">
+      <c r="L28" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B32" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="23"/>
-      <c r="B31" s="12" t="s">
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="30"/>
+      <c r="B33" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="23"/>
-      <c r="B32" s="12" t="s">
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="30"/>
+      <c r="B34" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B35" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="20"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="16"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="17"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="13"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="38"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="31"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="40"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="41"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="31"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="44"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B38" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="57"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="57"/>
+      <c r="B40" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="57"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="57"/>
+      <c r="B42" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="57"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="57"/>
+      <c r="B44" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="6" t="s">
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="57"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="57"/>
+      <c r="B46" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="57"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="57"/>
+      <c r="B48" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12" t="s">
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="57"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="57"/>
+      <c r="B50" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="12"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
+      <c r="K50" s="27"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27"/>
+      <c r="O50" s="27"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="57"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="57"/>
+      <c r="B52" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="57"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="29"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="57"/>
+      <c r="B54" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="57"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="57"/>
+      <c r="B56" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="57"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="57"/>
+      <c r="B58" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="57"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="O59" s="28"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="58"/>
+      <c r="B60" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="59"/>
+      <c r="M60" s="59"/>
+      <c r="N60" s="59"/>
+      <c r="O60" s="59"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="10"/>
-      <c r="B58" s="6" t="s">
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="26"/>
+      <c r="B62" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" s="10"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
-      <c r="B60" s="3" t="s">
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="26"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="29"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="26"/>
+      <c r="B64" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" s="10"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="26"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="29"/>
+      <c r="M65" s="29"/>
+      <c r="N65" s="29"/>
+      <c r="O65" s="29"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
-      <c r="N62" s="8"/>
-      <c r="O62" s="7"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="6" t="s">
+      <c r="B66" s="33"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="34"/>
+      <c r="M66" s="34"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="35"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="50"/>
+      <c r="B67" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-      <c r="B65" s="3" t="s">
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="50"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="50"/>
+      <c r="B69" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-      <c r="B67" s="3" t="s">
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="32"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="50"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="50"/>
+      <c r="B71" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="6"/>
-      <c r="O68" s="6"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-      <c r="B69" s="3" t="s">
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="50"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="29"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="29"/>
+      <c r="M72" s="29"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="29"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="50"/>
+      <c r="B73" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-      <c r="B71" s="3" t="s">
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
+      <c r="L73" s="32"/>
+      <c r="M73" s="32"/>
+      <c r="N73" s="32"/>
+      <c r="O73" s="32"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="50"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="28"/>
+      <c r="L74" s="28"/>
+      <c r="M74" s="28"/>
+      <c r="N74" s="28"/>
+      <c r="O74" s="28"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="50"/>
+      <c r="B75" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-      <c r="B73" s="3" t="s">
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="32"/>
+      <c r="M75" s="32"/>
+      <c r="N75" s="32"/>
+      <c r="O75" s="32"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="50"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="28"/>
+      <c r="J76" s="28"/>
+      <c r="K76" s="28"/>
+      <c r="L76" s="28"/>
+      <c r="M76" s="28"/>
+      <c r="N76" s="28"/>
+      <c r="O76" s="28"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="50"/>
+      <c r="B77" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-      <c r="B75" s="3" t="s">
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="32"/>
+      <c r="L77" s="32"/>
+      <c r="M77" s="32"/>
+      <c r="N77" s="32"/>
+      <c r="O77" s="32"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="50"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+      <c r="K78" s="28"/>
+      <c r="L78" s="28"/>
+      <c r="M78" s="28"/>
+      <c r="N78" s="28"/>
+      <c r="O78" s="28"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="50"/>
+      <c r="B79" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-      <c r="B77" s="3" t="s">
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
+      <c r="L79" s="32"/>
+      <c r="M79" s="32"/>
+      <c r="N79" s="32"/>
+      <c r="O79" s="32"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="50"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
+      <c r="L80" s="32"/>
+      <c r="M80" s="32"/>
+      <c r="N80" s="32"/>
+      <c r="O80" s="32"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="50"/>
+      <c r="B81" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
+      <c r="J81" s="32"/>
+      <c r="K81" s="32"/>
+      <c r="L81" s="32"/>
+      <c r="M81" s="32"/>
+      <c r="N81" s="32"/>
+      <c r="O81" s="32"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="50"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="32"/>
+      <c r="L82" s="32"/>
+      <c r="M82" s="32"/>
+      <c r="N82" s="32"/>
+      <c r="O82" s="32"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="50"/>
+      <c r="B83" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B79" s="1"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B80" s="2"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B82" s="2"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B84" s="2"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="32"/>
+      <c r="L83" s="32"/>
+      <c r="M83" s="32"/>
+      <c r="N83" s="32"/>
+      <c r="O83" s="32"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="51"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+      <c r="J84" s="32"/>
+      <c r="K84" s="32"/>
+      <c r="L84" s="32"/>
+      <c r="M84" s="32"/>
+      <c r="N84" s="32"/>
+      <c r="O84" s="32"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
     </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B88" s="2"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B89" s="1"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B91" s="1"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B93" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="A62:A78"/>
-    <mergeCell ref="B30:O30"/>
-    <mergeCell ref="B31:O31"/>
-    <mergeCell ref="B32:O32"/>
-    <mergeCell ref="B36:O36"/>
-    <mergeCell ref="B37:O37"/>
-    <mergeCell ref="B38:O38"/>
-    <mergeCell ref="B39:O39"/>
-    <mergeCell ref="B40:O40"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A56"/>
-    <mergeCell ref="B41:O41"/>
-    <mergeCell ref="B42:O42"/>
-    <mergeCell ref="B43:O43"/>
-    <mergeCell ref="B44:O44"/>
-    <mergeCell ref="B45:O45"/>
+  <mergeCells count="56">
+    <mergeCell ref="A66:A84"/>
+    <mergeCell ref="B59:O59"/>
+    <mergeCell ref="B60:O60"/>
+    <mergeCell ref="A38:A60"/>
+    <mergeCell ref="B83:O83"/>
+    <mergeCell ref="B84:O84"/>
+    <mergeCell ref="B35:O37"/>
+    <mergeCell ref="B75:O75"/>
+    <mergeCell ref="B76:O76"/>
+    <mergeCell ref="B77:O77"/>
+    <mergeCell ref="B78:O78"/>
+    <mergeCell ref="B79:O79"/>
+    <mergeCell ref="B80:O80"/>
+    <mergeCell ref="B69:O69"/>
+    <mergeCell ref="B81:O81"/>
+    <mergeCell ref="B82:O82"/>
+    <mergeCell ref="B70:O70"/>
+    <mergeCell ref="B71:O71"/>
+    <mergeCell ref="B72:O72"/>
+    <mergeCell ref="B73:O73"/>
+    <mergeCell ref="B74:O74"/>
+    <mergeCell ref="B51:O51"/>
+    <mergeCell ref="B52:O52"/>
+    <mergeCell ref="B53:O53"/>
+    <mergeCell ref="B54:O54"/>
+    <mergeCell ref="B68:O68"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="B56:O56"/>
+    <mergeCell ref="B57:O57"/>
+    <mergeCell ref="B58:O58"/>
+    <mergeCell ref="B61:O61"/>
+    <mergeCell ref="B62:O62"/>
+    <mergeCell ref="B63:O63"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B65:O65"/>
+    <mergeCell ref="B66:O66"/>
+    <mergeCell ref="B67:O67"/>
     <mergeCell ref="B46:O46"/>
     <mergeCell ref="B47:O47"/>
     <mergeCell ref="B48:O48"/>
     <mergeCell ref="B49:O49"/>
     <mergeCell ref="B50:O50"/>
-    <mergeCell ref="B51:O51"/>
-    <mergeCell ref="B52:O52"/>
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="B53:O53"/>
-    <mergeCell ref="B54:O54"/>
-    <mergeCell ref="B55:O55"/>
-    <mergeCell ref="B56:O56"/>
-    <mergeCell ref="B57:O57"/>
-    <mergeCell ref="B58:O58"/>
-    <mergeCell ref="B66:O66"/>
-    <mergeCell ref="B67:O67"/>
-    <mergeCell ref="B68:O68"/>
-    <mergeCell ref="B69:O69"/>
-    <mergeCell ref="B70:O70"/>
-    <mergeCell ref="B59:O59"/>
-    <mergeCell ref="B60:O60"/>
-    <mergeCell ref="B61:O61"/>
-    <mergeCell ref="B62:O62"/>
-    <mergeCell ref="B63:O63"/>
-    <mergeCell ref="B77:O77"/>
-    <mergeCell ref="B78:O78"/>
-    <mergeCell ref="B33:O35"/>
-    <mergeCell ref="B71:O71"/>
-    <mergeCell ref="B72:O72"/>
-    <mergeCell ref="B73:O73"/>
-    <mergeCell ref="B74:O74"/>
-    <mergeCell ref="B75:O75"/>
-    <mergeCell ref="B76:O76"/>
-    <mergeCell ref="B65:O65"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="B32:O32"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="B40:O40"/>
+    <mergeCell ref="B41:O41"/>
+    <mergeCell ref="B42:O42"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B43:O43"/>
+    <mergeCell ref="B44:O44"/>
+    <mergeCell ref="B45:O45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>